--- a/12626731.xlsx
+++ b/12626731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158E2A12-67D0-47F0-8FA7-DAE74DCD7A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE7587D-EB07-422E-BFCB-91E928A0786B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2141,7 +2141,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
         <v>46269</v>
       </c>
@@ -2183,29 +2183,55 @@
       <c r="M30" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="N30" s="17"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="12"/>
+      <c r="N30" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B31" s="14">
+        <v>450</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>180</v>
+      </c>
+      <c r="E31" s="14">
+        <v>20</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>60</v>
+      </c>
+      <c r="I31" s="15">
+        <f t="shared" ref="I31" si="38">IF(SUM(B31:F31,H31)=0,"",SUM(B31:F31,H31))</f>
+        <v>710</v>
+      </c>
+      <c r="J31" s="15">
+        <f t="shared" ref="J31" si="39">IF(I31="","",1440-I31)</f>
+        <v>730</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>
@@ -3053,11 +3079,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="38">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="40">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="39">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="41">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3075,11 +3101,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3097,11 +3123,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3119,11 +3145,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3141,11 +3167,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3163,11 +3189,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3185,11 +3211,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3207,11 +3233,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3229,11 +3255,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3251,11 +3277,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3273,11 +3299,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3295,11 +3321,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3317,11 +3343,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3339,11 +3365,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3361,11 +3387,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3383,11 +3409,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3405,11 +3431,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3427,11 +3453,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3449,11 +3475,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3471,11 +3497,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3493,11 +3519,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3515,11 +3541,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3537,11 +3563,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3559,11 +3585,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3581,11 +3607,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3603,11 +3629,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3625,11 +3651,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3647,11 +3673,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3669,11 +3695,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3691,11 +3717,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3713,11 +3739,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3735,11 +3761,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3757,11 +3783,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3779,11 +3805,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3801,11 +3827,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3823,11 +3849,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3845,11 +3871,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3867,11 +3893,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3889,11 +3915,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3911,11 +3937,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3933,11 +3959,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -3955,11 +3981,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -3977,11 +4003,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -3999,11 +4025,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -4021,11 +4047,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -4043,11 +4069,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -4065,11 +4091,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -4087,11 +4113,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -4109,11 +4135,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4131,11 +4157,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4153,11 +4179,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4175,11 +4201,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4197,11 +4223,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4219,11 +4245,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4241,11 +4267,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4263,11 +4289,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4285,11 +4311,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4307,11 +4333,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4329,11 +4355,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4351,11 +4377,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4373,11 +4399,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4395,11 +4421,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4417,11 +4443,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4439,11 +4465,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4461,11 +4487,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="40">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="42">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="41">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="43">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4483,11 +4509,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4505,11 +4531,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4527,11 +4553,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4549,11 +4575,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4571,11 +4597,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4593,11 +4619,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4615,11 +4641,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4637,11 +4663,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4659,11 +4685,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4681,11 +4707,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4703,11 +4729,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4725,11 +4751,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4747,11 +4773,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4769,11 +4795,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4791,11 +4817,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4813,11 +4839,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4835,11 +4861,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4857,11 +4883,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4879,11 +4905,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -4901,11 +4927,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -4923,11 +4949,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -4945,11 +4971,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -4967,11 +4993,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -4989,11 +5015,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -5011,11 +5037,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -5033,11 +5059,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -5055,11 +5081,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5077,11 +5103,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5099,11 +5125,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5121,11 +5147,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5143,11 +5169,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5165,11 +5191,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5187,11 +5213,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5209,11 +5235,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5231,11 +5257,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5253,11 +5279,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5275,11 +5301,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5297,11 +5323,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5319,11 +5345,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5341,11 +5367,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5363,11 +5389,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5385,11 +5411,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5407,11 +5433,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5429,11 +5455,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5451,11 +5477,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5473,11 +5499,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5495,11 +5521,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5517,11 +5543,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5539,11 +5565,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5561,11 +5587,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5583,11 +5609,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5605,11 +5631,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5627,11 +5653,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5649,11 +5675,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5671,11 +5697,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5693,11 +5719,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5715,11 +5741,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5737,11 +5763,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5759,11 +5785,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5781,11 +5807,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5803,11 +5829,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5825,11 +5851,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5847,11 +5873,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5869,11 +5895,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="42">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="44">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="43">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="45">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5891,11 +5917,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -5913,11 +5939,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -5935,11 +5961,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -5957,11 +5983,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -5979,11 +6005,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -6001,11 +6027,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -6023,11 +6049,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -6045,11 +6071,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -6067,11 +6093,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6089,11 +6115,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6111,11 +6137,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6133,11 +6159,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6155,11 +6181,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6177,11 +6203,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6199,11 +6225,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6221,11 +6247,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6243,11 +6269,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6265,11 +6291,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6287,11 +6313,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6309,11 +6335,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6331,11 +6357,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6353,11 +6379,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6375,11 +6401,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6397,11 +6423,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6419,11 +6445,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6441,11 +6467,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6463,11 +6489,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6485,11 +6511,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6507,11 +6533,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6529,11 +6555,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6551,11 +6577,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6573,11 +6599,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6595,11 +6621,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6617,11 +6643,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6639,11 +6665,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6661,11 +6687,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6683,11 +6709,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6705,11 +6731,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6727,11 +6753,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6749,11 +6775,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6771,11 +6797,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6793,11 +6819,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6815,11 +6841,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6837,11 +6863,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6859,11 +6885,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6881,11 +6907,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -6903,11 +6929,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -6925,11 +6951,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -6947,11 +6973,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -6969,11 +6995,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -6991,11 +7017,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -7013,11 +7039,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -7035,11 +7061,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -7057,11 +7083,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7079,11 +7105,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7101,11 +7127,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7123,11 +7149,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7145,11 +7171,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7167,11 +7193,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7189,11 +7215,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7211,11 +7237,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7233,11 +7259,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7255,11 +7281,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7277,11 +7303,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="44">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="46">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="45">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="47">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7299,11 +7325,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7321,11 +7347,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7343,11 +7369,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7365,11 +7391,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7387,11 +7413,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7409,11 +7435,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7431,11 +7457,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7453,11 +7479,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7475,11 +7501,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7497,11 +7523,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7519,11 +7545,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7541,11 +7567,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7563,11 +7589,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7585,11 +7611,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7607,11 +7633,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7629,11 +7655,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7651,11 +7677,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7673,11 +7699,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7695,11 +7721,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7717,11 +7743,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7739,11 +7765,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7761,11 +7787,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7783,11 +7809,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7805,11 +7831,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7827,11 +7853,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7849,11 +7875,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7871,11 +7897,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7893,11 +7919,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -7915,11 +7941,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -7937,11 +7963,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -7959,11 +7985,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -7981,11 +8007,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -8003,11 +8029,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -8025,11 +8051,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -8047,11 +8073,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -8069,11 +8095,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8091,11 +8117,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8113,11 +8139,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8135,11 +8161,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8157,11 +8183,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8179,11 +8205,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8201,11 +8227,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8223,11 +8249,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8245,11 +8271,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8267,11 +8293,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8289,11 +8315,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8311,11 +8337,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8333,11 +8359,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8355,11 +8381,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8377,11 +8403,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8399,11 +8425,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8421,11 +8447,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8443,11 +8469,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8465,11 +8491,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8487,11 +8513,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8509,11 +8535,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8531,11 +8557,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8553,11 +8579,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8575,11 +8601,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8597,11 +8623,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8619,11 +8645,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8641,11 +8667,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8663,11 +8689,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8685,11 +8711,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="46">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="48">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="47">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="49">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8707,11 +8733,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8729,11 +8755,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8751,11 +8777,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8773,11 +8799,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8795,11 +8821,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8817,11 +8843,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8839,11 +8865,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8861,11 +8887,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8883,11 +8909,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -8905,11 +8931,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -8927,11 +8953,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -8949,11 +8975,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -8971,11 +8997,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -8993,11 +9019,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -9015,11 +9041,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -9037,11 +9063,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -9059,11 +9085,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9081,11 +9107,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9103,11 +9129,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9125,11 +9151,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9147,11 +9173,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9169,11 +9195,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9191,11 +9217,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9213,11 +9239,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9235,11 +9261,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9257,11 +9283,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9279,11 +9305,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9301,11 +9327,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9323,11 +9349,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9345,11 +9371,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9367,11 +9393,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9389,11 +9415,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9411,11 +9437,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9433,11 +9459,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9455,11 +9481,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9477,11 +9503,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9499,11 +9525,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9521,11 +9547,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9543,11 +9569,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9565,11 +9591,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9587,11 +9613,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9609,11 +9635,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9631,11 +9657,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9653,11 +9679,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9675,11 +9701,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9697,11 +9723,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9719,11 +9745,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9741,11 +9767,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9763,11 +9789,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9785,11 +9811,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9807,11 +9833,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9829,11 +9855,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9851,11 +9877,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9873,11 +9899,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9895,11 +9921,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -9917,11 +9943,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -9939,11 +9965,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -9961,11 +9987,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -9983,11 +10009,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -10005,11 +10031,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10027,11 +10053,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10049,11 +10075,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10071,11 +10097,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10093,11 +10119,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="48">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="50">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="49">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="51">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10115,11 +10141,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10137,11 +10163,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10159,11 +10185,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10181,11 +10207,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10203,11 +10229,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10225,11 +10251,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10247,11 +10273,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10269,11 +10295,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10291,11 +10317,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10313,11 +10339,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10335,11 +10361,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12626731.xlsx
+++ b/12626731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE7587D-EB07-422E-BFCB-91E928A0786B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1EFA95-97DC-4F49-90F7-2053821AFE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>Today, I worked on College Subjects.</t>
+  </si>
+  <si>
+    <t>Today, I worked on College Subjects for CA.</t>
   </si>
 </sst>
 </file>
@@ -2233,27 +2236,51 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="12"/>
+    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B32" s="14">
+        <v>450</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>200</v>
+      </c>
+      <c r="E32" s="14">
+        <v>20</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>60</v>
+      </c>
+      <c r="I32" s="15">
+        <f t="shared" ref="I32" si="40">IF(SUM(B32:F32,H32)=0,"",SUM(B32:F32,H32))</f>
+        <v>730</v>
+      </c>
+      <c r="J32" s="15">
+        <f t="shared" ref="J32" si="41">IF(I32="","",1440-I32)</f>
+        <v>710</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>
@@ -3079,11 +3106,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="40">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="42">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="41">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="43">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3101,11 +3128,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3123,11 +3150,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3145,11 +3172,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3167,11 +3194,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3189,11 +3216,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3211,11 +3238,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3233,11 +3260,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3255,11 +3282,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3277,11 +3304,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3299,11 +3326,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3321,11 +3348,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3343,11 +3370,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3365,11 +3392,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3387,11 +3414,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3409,11 +3436,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3431,11 +3458,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3453,11 +3480,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3475,11 +3502,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3497,11 +3524,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3519,11 +3546,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3541,11 +3568,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3563,11 +3590,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3585,11 +3612,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3607,11 +3634,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3629,11 +3656,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3651,11 +3678,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3673,11 +3700,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3695,11 +3722,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3717,11 +3744,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3739,11 +3766,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3761,11 +3788,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3783,11 +3810,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3805,11 +3832,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3827,11 +3854,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3849,11 +3876,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3871,11 +3898,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3893,11 +3920,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3915,11 +3942,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3937,11 +3964,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3959,11 +3986,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -3981,11 +4008,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -4003,11 +4030,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -4025,11 +4052,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -4047,11 +4074,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -4069,11 +4096,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -4091,11 +4118,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -4113,11 +4140,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -4135,11 +4162,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4157,11 +4184,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4179,11 +4206,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4201,11 +4228,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4223,11 +4250,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4245,11 +4272,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4267,11 +4294,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4289,11 +4316,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4311,11 +4338,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4333,11 +4360,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4355,11 +4382,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4377,11 +4404,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4399,11 +4426,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4421,11 +4448,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4443,11 +4470,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4465,11 +4492,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4487,11 +4514,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="42">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="44">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="43">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="45">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4509,11 +4536,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4531,11 +4558,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4553,11 +4580,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4575,11 +4602,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4597,11 +4624,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4619,11 +4646,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4641,11 +4668,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4663,11 +4690,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4685,11 +4712,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4707,11 +4734,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4729,11 +4756,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4751,11 +4778,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4773,11 +4800,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4795,11 +4822,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4817,11 +4844,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4839,11 +4866,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4861,11 +4888,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4883,11 +4910,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4905,11 +4932,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -4927,11 +4954,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -4949,11 +4976,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -4971,11 +4998,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -4993,11 +5020,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -5015,11 +5042,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -5037,11 +5064,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -5059,11 +5086,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -5081,11 +5108,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5103,11 +5130,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5125,11 +5152,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5147,11 +5174,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5169,11 +5196,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5191,11 +5218,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5213,11 +5240,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5235,11 +5262,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5257,11 +5284,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5279,11 +5306,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5301,11 +5328,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5323,11 +5350,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5345,11 +5372,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5367,11 +5394,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5389,11 +5416,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5411,11 +5438,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5433,11 +5460,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5455,11 +5482,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5477,11 +5504,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5499,11 +5526,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5521,11 +5548,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5543,11 +5570,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5565,11 +5592,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5587,11 +5614,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5609,11 +5636,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5631,11 +5658,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5653,11 +5680,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5675,11 +5702,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5697,11 +5724,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5719,11 +5746,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5741,11 +5768,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5763,11 +5790,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5785,11 +5812,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5807,11 +5834,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5829,11 +5856,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5851,11 +5878,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5873,11 +5900,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5895,11 +5922,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="44">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="46">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="45">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="47">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5917,11 +5944,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -5939,11 +5966,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -5961,11 +5988,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -5983,11 +6010,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -6005,11 +6032,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -6027,11 +6054,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -6049,11 +6076,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -6071,11 +6098,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -6093,11 +6120,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6115,11 +6142,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6137,11 +6164,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6159,11 +6186,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6181,11 +6208,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6203,11 +6230,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6225,11 +6252,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6247,11 +6274,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6269,11 +6296,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6291,11 +6318,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6313,11 +6340,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6335,11 +6362,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6357,11 +6384,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6379,11 +6406,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6401,11 +6428,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6423,11 +6450,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6445,11 +6472,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6467,11 +6494,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6489,11 +6516,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6511,11 +6538,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6533,11 +6560,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6555,11 +6582,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6577,11 +6604,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6599,11 +6626,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6621,11 +6648,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6643,11 +6670,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6665,11 +6692,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6687,11 +6714,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6709,11 +6736,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6731,11 +6758,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6753,11 +6780,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6775,11 +6802,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6797,11 +6824,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6819,11 +6846,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6841,11 +6868,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6863,11 +6890,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6885,11 +6912,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6907,11 +6934,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -6929,11 +6956,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -6951,11 +6978,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -6973,11 +7000,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -6995,11 +7022,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -7017,11 +7044,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -7039,11 +7066,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -7061,11 +7088,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -7083,11 +7110,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7105,11 +7132,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7127,11 +7154,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7149,11 +7176,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7171,11 +7198,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7193,11 +7220,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7215,11 +7242,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7237,11 +7264,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7259,11 +7286,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7281,11 +7308,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7303,11 +7330,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="46">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="48">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="47">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="49">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7325,11 +7352,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7347,11 +7374,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7369,11 +7396,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7391,11 +7418,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7413,11 +7440,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7435,11 +7462,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7457,11 +7484,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7479,11 +7506,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7501,11 +7528,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7523,11 +7550,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7545,11 +7572,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7567,11 +7594,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7589,11 +7616,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7611,11 +7638,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7633,11 +7660,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7655,11 +7682,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7677,11 +7704,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7699,11 +7726,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7721,11 +7748,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7743,11 +7770,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7765,11 +7792,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7787,11 +7814,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7809,11 +7836,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7831,11 +7858,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7853,11 +7880,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7875,11 +7902,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7897,11 +7924,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7919,11 +7946,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -7941,11 +7968,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -7963,11 +7990,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -7985,11 +8012,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -8007,11 +8034,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -8029,11 +8056,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -8051,11 +8078,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -8073,11 +8100,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -8095,11 +8122,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8117,11 +8144,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8139,11 +8166,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8161,11 +8188,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8183,11 +8210,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8205,11 +8232,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8227,11 +8254,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8249,11 +8276,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8271,11 +8298,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8293,11 +8320,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8315,11 +8342,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8337,11 +8364,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8359,11 +8386,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8381,11 +8408,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8403,11 +8430,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8425,11 +8452,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8447,11 +8474,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8469,11 +8496,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8491,11 +8518,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8513,11 +8540,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8535,11 +8562,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8557,11 +8584,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8579,11 +8606,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8601,11 +8628,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8623,11 +8650,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8645,11 +8672,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8667,11 +8694,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8689,11 +8716,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8711,11 +8738,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="48">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="50">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="49">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="51">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8733,11 +8760,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8755,11 +8782,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8777,11 +8804,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8799,11 +8826,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8821,11 +8848,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8843,11 +8870,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8865,11 +8892,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8887,11 +8914,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8909,11 +8936,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -8931,11 +8958,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -8953,11 +8980,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -8975,11 +9002,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -8997,11 +9024,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -9019,11 +9046,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -9041,11 +9068,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -9063,11 +9090,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -9085,11 +9112,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9107,11 +9134,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9129,11 +9156,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9151,11 +9178,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9173,11 +9200,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9195,11 +9222,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9217,11 +9244,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9239,11 +9266,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9261,11 +9288,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9283,11 +9310,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9305,11 +9332,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9327,11 +9354,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9349,11 +9376,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9371,11 +9398,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9393,11 +9420,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9415,11 +9442,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9437,11 +9464,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9459,11 +9486,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9481,11 +9508,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9503,11 +9530,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9525,11 +9552,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9547,11 +9574,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9569,11 +9596,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9591,11 +9618,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9613,11 +9640,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9635,11 +9662,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9657,11 +9684,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9679,11 +9706,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9701,11 +9728,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9723,11 +9750,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9745,11 +9772,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9767,11 +9794,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9789,11 +9816,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9811,11 +9838,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9833,11 +9860,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9855,11 +9882,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9877,11 +9904,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9899,11 +9926,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9921,11 +9948,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -9943,11 +9970,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -9965,11 +9992,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -9987,11 +10014,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -10009,11 +10036,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -10031,11 +10058,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10053,11 +10080,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10075,11 +10102,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10097,11 +10124,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10119,11 +10146,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="50">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="52">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="51">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="53">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10141,11 +10168,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10163,11 +10190,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10185,11 +10212,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10207,11 +10234,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10229,11 +10256,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10251,11 +10278,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10273,11 +10300,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10295,11 +10322,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10317,11 +10344,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10339,11 +10366,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10361,11 +10388,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12626731.xlsx
+++ b/12626731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1EFA95-97DC-4F49-90F7-2053821AFE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB23E4DF-28D7-4453-B2E7-6987F4B37027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2282,27 +2282,51 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="12"/>
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B33" s="14">
+        <v>450</v>
+      </c>
+      <c r="C33" s="14">
+        <v>20</v>
+      </c>
+      <c r="D33" s="14">
+        <v>180</v>
+      </c>
+      <c r="E33" s="14">
+        <v>15</v>
+      </c>
+      <c r="F33" s="14">
+        <v>350</v>
+      </c>
+      <c r="G33" s="14">
+        <v>7</v>
+      </c>
+      <c r="H33" s="14">
+        <v>60</v>
+      </c>
+      <c r="I33" s="15">
+        <f t="shared" ref="I33" si="42">IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
+        <v>1075</v>
+      </c>
+      <c r="J33" s="15">
+        <f t="shared" ref="J33" si="43">IF(I33="","",1440-I33)</f>
+        <v>365</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
@@ -3106,11 +3130,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="42">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="44">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="43">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="45">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3128,11 +3152,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3150,11 +3174,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3172,11 +3196,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3194,11 +3218,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3216,11 +3240,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3238,11 +3262,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3260,11 +3284,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3282,11 +3306,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3304,11 +3328,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3326,11 +3350,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3348,11 +3372,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3370,11 +3394,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3392,11 +3416,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3414,11 +3438,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3436,11 +3460,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3458,11 +3482,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3480,11 +3504,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3502,11 +3526,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3524,11 +3548,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3546,11 +3570,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3568,11 +3592,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3590,11 +3614,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3612,11 +3636,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3634,11 +3658,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3656,11 +3680,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3678,11 +3702,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3700,11 +3724,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3722,11 +3746,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3744,11 +3768,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3766,11 +3790,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3788,11 +3812,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3810,11 +3834,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3832,11 +3856,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3854,11 +3878,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3876,11 +3900,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3898,11 +3922,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3920,11 +3944,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3942,11 +3966,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3964,11 +3988,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3986,11 +4010,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -4008,11 +4032,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -4030,11 +4054,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -4052,11 +4076,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -4074,11 +4098,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -4096,11 +4120,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -4118,11 +4142,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -4140,11 +4164,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -4162,11 +4186,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4184,11 +4208,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4206,11 +4230,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4228,11 +4252,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4250,11 +4274,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4272,11 +4296,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4294,11 +4318,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4316,11 +4340,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4338,11 +4362,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4360,11 +4384,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4382,11 +4406,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4404,11 +4428,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4426,11 +4450,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4448,11 +4472,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4470,11 +4494,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4492,11 +4516,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4514,11 +4538,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="44">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="46">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="45">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="47">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4536,11 +4560,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4558,11 +4582,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4580,11 +4604,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4602,11 +4626,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4624,11 +4648,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4646,11 +4670,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4668,11 +4692,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4690,11 +4714,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4712,11 +4736,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4734,11 +4758,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4756,11 +4780,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4778,11 +4802,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4800,11 +4824,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4822,11 +4846,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4844,11 +4868,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4866,11 +4890,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4888,11 +4912,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4910,11 +4934,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4932,11 +4956,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -4954,11 +4978,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -4976,11 +5000,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -4998,11 +5022,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -5020,11 +5044,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -5042,11 +5066,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -5064,11 +5088,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -5086,11 +5110,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -5108,11 +5132,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5130,11 +5154,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5152,11 +5176,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5174,11 +5198,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5196,11 +5220,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5218,11 +5242,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5240,11 +5264,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5262,11 +5286,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5284,11 +5308,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5306,11 +5330,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5328,11 +5352,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5350,11 +5374,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5372,11 +5396,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5394,11 +5418,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5416,11 +5440,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5438,11 +5462,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5460,11 +5484,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5482,11 +5506,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5504,11 +5528,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5526,11 +5550,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5548,11 +5572,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5570,11 +5594,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5592,11 +5616,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5614,11 +5638,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5636,11 +5660,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5658,11 +5682,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5680,11 +5704,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5702,11 +5726,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5724,11 +5748,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5746,11 +5770,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5768,11 +5792,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5790,11 +5814,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5812,11 +5836,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5834,11 +5858,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5856,11 +5880,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5878,11 +5902,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5900,11 +5924,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5922,11 +5946,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="46">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="48">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="47">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="49">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5944,11 +5968,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -5966,11 +5990,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -5988,11 +6012,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -6010,11 +6034,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -6032,11 +6056,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -6054,11 +6078,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -6076,11 +6100,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -6098,11 +6122,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -6120,11 +6144,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6142,11 +6166,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6164,11 +6188,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6186,11 +6210,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6208,11 +6232,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6230,11 +6254,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6252,11 +6276,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6274,11 +6298,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6296,11 +6320,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6318,11 +6342,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6340,11 +6364,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6362,11 +6386,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6384,11 +6408,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6406,11 +6430,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6428,11 +6452,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6450,11 +6474,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6472,11 +6496,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6494,11 +6518,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6516,11 +6540,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6538,11 +6562,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6560,11 +6584,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6582,11 +6606,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6604,11 +6628,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6626,11 +6650,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6648,11 +6672,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6670,11 +6694,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6692,11 +6716,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6714,11 +6738,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6736,11 +6760,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6758,11 +6782,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6780,11 +6804,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6802,11 +6826,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6824,11 +6848,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6846,11 +6870,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6868,11 +6892,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6890,11 +6914,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6912,11 +6936,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6934,11 +6958,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -6956,11 +6980,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -6978,11 +7002,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -7000,11 +7024,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -7022,11 +7046,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -7044,11 +7068,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -7066,11 +7090,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -7088,11 +7112,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -7110,11 +7134,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7132,11 +7156,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7154,11 +7178,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7176,11 +7200,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7198,11 +7222,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7220,11 +7244,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7242,11 +7266,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7264,11 +7288,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7286,11 +7310,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7308,11 +7332,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7330,11 +7354,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="48">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="50">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="49">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="51">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7352,11 +7376,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7374,11 +7398,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7396,11 +7420,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7418,11 +7442,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7440,11 +7464,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7462,11 +7486,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7484,11 +7508,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7506,11 +7530,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7528,11 +7552,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7550,11 +7574,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7572,11 +7596,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7594,11 +7618,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7616,11 +7640,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7638,11 +7662,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7660,11 +7684,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7682,11 +7706,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7704,11 +7728,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7726,11 +7750,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7748,11 +7772,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7770,11 +7794,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7792,11 +7816,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7814,11 +7838,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7836,11 +7860,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7858,11 +7882,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7880,11 +7904,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7902,11 +7926,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7924,11 +7948,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7946,11 +7970,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -7968,11 +7992,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -7990,11 +8014,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -8012,11 +8036,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -8034,11 +8058,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -8056,11 +8080,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -8078,11 +8102,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -8100,11 +8124,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -8122,11 +8146,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8144,11 +8168,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8166,11 +8190,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8188,11 +8212,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8210,11 +8234,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8232,11 +8256,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8254,11 +8278,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8276,11 +8300,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8298,11 +8322,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8320,11 +8344,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8342,11 +8366,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8364,11 +8388,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8386,11 +8410,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8408,11 +8432,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8430,11 +8454,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8452,11 +8476,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8474,11 +8498,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8496,11 +8520,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8518,11 +8542,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8540,11 +8564,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8562,11 +8586,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8584,11 +8608,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8606,11 +8630,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8628,11 +8652,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8650,11 +8674,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8672,11 +8696,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8694,11 +8718,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8716,11 +8740,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8738,11 +8762,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="50">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="52">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="51">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="53">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8760,11 +8784,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8782,11 +8806,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8804,11 +8828,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8826,11 +8850,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8848,11 +8872,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8870,11 +8894,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8892,11 +8916,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8914,11 +8938,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8936,11 +8960,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -8958,11 +8982,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -8980,11 +9004,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -9002,11 +9026,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -9024,11 +9048,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -9046,11 +9070,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -9068,11 +9092,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -9090,11 +9114,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -9112,11 +9136,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9134,11 +9158,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9156,11 +9180,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9178,11 +9202,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9200,11 +9224,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9222,11 +9246,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9244,11 +9268,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9266,11 +9290,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9288,11 +9312,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9310,11 +9334,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9332,11 +9356,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9354,11 +9378,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9376,11 +9400,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9398,11 +9422,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9420,11 +9444,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9442,11 +9466,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9464,11 +9488,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9486,11 +9510,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9508,11 +9532,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9530,11 +9554,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9552,11 +9576,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9574,11 +9598,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9596,11 +9620,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9618,11 +9642,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9640,11 +9664,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9662,11 +9686,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9684,11 +9708,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9706,11 +9730,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9728,11 +9752,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9750,11 +9774,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9772,11 +9796,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9794,11 +9818,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9816,11 +9840,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9838,11 +9862,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9860,11 +9884,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9882,11 +9906,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9904,11 +9928,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9926,11 +9950,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9948,11 +9972,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -9970,11 +9994,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -9992,11 +10016,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -10014,11 +10038,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -10036,11 +10060,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -10058,11 +10082,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10080,11 +10104,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10102,11 +10126,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10124,11 +10148,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10146,11 +10170,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="52">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="54">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="53">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="55">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10168,11 +10192,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10190,11 +10214,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10212,11 +10236,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10234,11 +10258,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10256,11 +10280,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10278,11 +10302,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10300,11 +10324,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10322,11 +10346,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10344,11 +10368,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10366,11 +10390,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10388,11 +10412,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12626731.xlsx
+++ b/12626731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB23E4DF-28D7-4453-B2E7-6987F4B37027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D991C0-D824-4EA3-9FD3-F6A1415D60D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>Today, I worked on College Subjects for CA.</t>
+  </si>
+  <si>
+    <t>Today, I worked on College Subjects  and Coding.</t>
   </si>
 </sst>
 </file>
@@ -2328,27 +2331,51 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="12"/>
+    <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B34" s="14">
+        <v>450</v>
+      </c>
+      <c r="C34" s="14">
+        <v>20</v>
+      </c>
+      <c r="D34" s="14">
+        <v>120</v>
+      </c>
+      <c r="E34" s="14">
+        <v>120</v>
+      </c>
+      <c r="F34" s="14">
+        <v>300</v>
+      </c>
+      <c r="G34" s="14">
+        <v>6</v>
+      </c>
+      <c r="H34" s="14">
+        <v>60</v>
+      </c>
+      <c r="I34" s="15">
+        <f t="shared" ref="I34" si="44">IF(SUM(B34:F34,H34)=0,"",SUM(B34:F34,H34))</f>
+        <v>1070</v>
+      </c>
+      <c r="J34" s="15">
+        <f t="shared" ref="J34" si="45">IF(I34="","",1440-I34)</f>
+        <v>370</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="8"/>
@@ -3130,11 +3157,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="44">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="46">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="45">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="47">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3152,11 +3179,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3174,11 +3201,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3196,11 +3223,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3218,11 +3245,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3240,11 +3267,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3262,11 +3289,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3284,11 +3311,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3306,11 +3333,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3328,11 +3355,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3350,11 +3377,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3372,11 +3399,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3394,11 +3421,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3416,11 +3443,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3438,11 +3465,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3460,11 +3487,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3482,11 +3509,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3504,11 +3531,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3526,11 +3553,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3548,11 +3575,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3570,11 +3597,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3592,11 +3619,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3614,11 +3641,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3636,11 +3663,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3658,11 +3685,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3680,11 +3707,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3702,11 +3729,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3724,11 +3751,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3746,11 +3773,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3768,11 +3795,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3790,11 +3817,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3812,11 +3839,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3834,11 +3861,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3856,11 +3883,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3878,11 +3905,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3900,11 +3927,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3922,11 +3949,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3944,11 +3971,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3966,11 +3993,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3988,11 +4015,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -4010,11 +4037,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -4032,11 +4059,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -4054,11 +4081,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -4076,11 +4103,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -4098,11 +4125,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -4120,11 +4147,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -4142,11 +4169,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -4164,11 +4191,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -4186,11 +4213,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4208,11 +4235,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4230,11 +4257,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4252,11 +4279,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4274,11 +4301,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4296,11 +4323,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4318,11 +4345,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4340,11 +4367,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4362,11 +4389,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4384,11 +4411,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4406,11 +4433,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4428,11 +4455,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4450,11 +4477,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4472,11 +4499,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4494,11 +4521,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4516,11 +4543,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4538,11 +4565,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="46">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="48">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="47">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="49">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4560,11 +4587,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4582,11 +4609,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4604,11 +4631,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4626,11 +4653,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4648,11 +4675,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4670,11 +4697,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4692,11 +4719,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4714,11 +4741,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4736,11 +4763,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4758,11 +4785,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4780,11 +4807,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4802,11 +4829,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4824,11 +4851,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4846,11 +4873,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4868,11 +4895,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4890,11 +4917,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4912,11 +4939,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4934,11 +4961,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4956,11 +4983,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -4978,11 +5005,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -5000,11 +5027,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -5022,11 +5049,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -5044,11 +5071,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -5066,11 +5093,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -5088,11 +5115,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -5110,11 +5137,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -5132,11 +5159,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5154,11 +5181,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5176,11 +5203,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5198,11 +5225,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5220,11 +5247,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5242,11 +5269,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5264,11 +5291,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5286,11 +5313,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5308,11 +5335,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5330,11 +5357,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5352,11 +5379,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5374,11 +5401,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5396,11 +5423,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5418,11 +5445,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5440,11 +5467,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5462,11 +5489,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5484,11 +5511,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5506,11 +5533,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5528,11 +5555,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5550,11 +5577,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5572,11 +5599,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5594,11 +5621,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5616,11 +5643,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5638,11 +5665,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5660,11 +5687,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5682,11 +5709,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5704,11 +5731,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5726,11 +5753,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5748,11 +5775,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5770,11 +5797,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5792,11 +5819,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5814,11 +5841,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5836,11 +5863,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5858,11 +5885,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5880,11 +5907,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5902,11 +5929,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5924,11 +5951,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5946,11 +5973,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="48">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="50">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="49">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="51">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5968,11 +5995,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -5990,11 +6017,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -6012,11 +6039,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -6034,11 +6061,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -6056,11 +6083,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -6078,11 +6105,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -6100,11 +6127,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -6122,11 +6149,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -6144,11 +6171,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6166,11 +6193,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6188,11 +6215,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6210,11 +6237,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6232,11 +6259,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6254,11 +6281,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6276,11 +6303,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6298,11 +6325,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6320,11 +6347,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6342,11 +6369,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6364,11 +6391,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6386,11 +6413,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6408,11 +6435,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6430,11 +6457,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6452,11 +6479,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6474,11 +6501,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6496,11 +6523,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6518,11 +6545,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6540,11 +6567,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6562,11 +6589,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6584,11 +6611,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6606,11 +6633,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6628,11 +6655,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6650,11 +6677,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6672,11 +6699,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6694,11 +6721,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6716,11 +6743,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6738,11 +6765,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6760,11 +6787,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6782,11 +6809,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6804,11 +6831,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6826,11 +6853,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6848,11 +6875,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6870,11 +6897,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6892,11 +6919,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6914,11 +6941,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6936,11 +6963,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6958,11 +6985,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -6980,11 +7007,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -7002,11 +7029,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -7024,11 +7051,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -7046,11 +7073,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -7068,11 +7095,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -7090,11 +7117,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -7112,11 +7139,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -7134,11 +7161,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7156,11 +7183,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7178,11 +7205,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7200,11 +7227,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7222,11 +7249,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7244,11 +7271,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7266,11 +7293,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7288,11 +7315,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7310,11 +7337,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7332,11 +7359,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7354,11 +7381,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="50">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="52">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="51">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="53">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7376,11 +7403,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7398,11 +7425,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7420,11 +7447,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7442,11 +7469,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7464,11 +7491,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7486,11 +7513,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7508,11 +7535,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7530,11 +7557,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7552,11 +7579,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7574,11 +7601,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7596,11 +7623,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7618,11 +7645,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7640,11 +7667,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7662,11 +7689,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7684,11 +7711,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7706,11 +7733,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7728,11 +7755,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7750,11 +7777,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7772,11 +7799,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7794,11 +7821,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7816,11 +7843,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7838,11 +7865,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7860,11 +7887,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7882,11 +7909,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7904,11 +7931,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7926,11 +7953,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7948,11 +7975,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7970,11 +7997,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -7992,11 +8019,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -8014,11 +8041,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -8036,11 +8063,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -8058,11 +8085,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -8080,11 +8107,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -8102,11 +8129,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -8124,11 +8151,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -8146,11 +8173,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8168,11 +8195,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8190,11 +8217,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8212,11 +8239,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8234,11 +8261,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8256,11 +8283,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8278,11 +8305,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8300,11 +8327,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8322,11 +8349,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8344,11 +8371,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8366,11 +8393,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8388,11 +8415,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8410,11 +8437,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8432,11 +8459,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8454,11 +8481,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8476,11 +8503,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8498,11 +8525,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8520,11 +8547,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8542,11 +8569,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8564,11 +8591,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8586,11 +8613,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8608,11 +8635,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8630,11 +8657,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8652,11 +8679,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8674,11 +8701,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8696,11 +8723,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8718,11 +8745,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8740,11 +8767,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8762,11 +8789,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="52">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="54">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="53">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="55">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8784,11 +8811,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8806,11 +8833,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8828,11 +8855,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8850,11 +8877,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8872,11 +8899,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8894,11 +8921,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8916,11 +8943,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8938,11 +8965,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8960,11 +8987,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -8982,11 +9009,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -9004,11 +9031,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -9026,11 +9053,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -9048,11 +9075,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -9070,11 +9097,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -9092,11 +9119,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -9114,11 +9141,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -9136,11 +9163,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9158,11 +9185,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9180,11 +9207,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9202,11 +9229,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9224,11 +9251,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9246,11 +9273,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9268,11 +9295,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9290,11 +9317,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9312,11 +9339,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9334,11 +9361,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9356,11 +9383,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9378,11 +9405,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9400,11 +9427,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9422,11 +9449,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9444,11 +9471,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9466,11 +9493,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9488,11 +9515,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9510,11 +9537,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9532,11 +9559,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9554,11 +9581,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9576,11 +9603,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9598,11 +9625,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9620,11 +9647,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9642,11 +9669,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9664,11 +9691,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9686,11 +9713,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9708,11 +9735,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9730,11 +9757,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9752,11 +9779,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9774,11 +9801,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9796,11 +9823,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9818,11 +9845,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9840,11 +9867,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9862,11 +9889,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9884,11 +9911,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9906,11 +9933,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9928,11 +9955,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9950,11 +9977,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9972,11 +9999,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -9994,11 +10021,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -10016,11 +10043,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -10038,11 +10065,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -10060,11 +10087,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -10082,11 +10109,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10104,11 +10131,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10126,11 +10153,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10148,11 +10175,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10170,11 +10197,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="54">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="56">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="55">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="57">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10192,11 +10219,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10214,11 +10241,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10236,11 +10263,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10258,11 +10285,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10280,11 +10307,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10302,11 +10329,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10324,11 +10351,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10346,11 +10373,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10368,11 +10395,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10390,11 +10417,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10412,11 +10439,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12626731.xlsx
+++ b/12626731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D991C0-D824-4EA3-9FD3-F6A1415D60D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122F94BD-4816-43E6-A12D-003D29EF598B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>Today, I worked on College Subjects  and Coding.</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -2377,27 +2380,51 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="12"/>
+    <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B35" s="14">
+        <v>450</v>
+      </c>
+      <c r="C35" s="14">
+        <v>20</v>
+      </c>
+      <c r="D35" s="14">
+        <v>0</v>
+      </c>
+      <c r="E35" s="14">
+        <v>30</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>60</v>
+      </c>
+      <c r="I35" s="15">
+        <f t="shared" ref="I35" si="46">IF(SUM(B35:F35,H35)=0,"",SUM(B35:F35,H35))</f>
+        <v>910</v>
+      </c>
+      <c r="J35" s="15">
+        <f t="shared" ref="J35" si="47">IF(I35="","",1440-I35)</f>
+        <v>530</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>
@@ -3157,11 +3184,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="46">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="48">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="47">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="49">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3179,11 +3206,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3201,11 +3228,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3223,11 +3250,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3245,11 +3272,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3267,11 +3294,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3289,11 +3316,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3311,11 +3338,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3333,11 +3360,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3355,11 +3382,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3377,11 +3404,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3399,11 +3426,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3421,11 +3448,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3443,11 +3470,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3465,11 +3492,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3487,11 +3514,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3509,11 +3536,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3531,11 +3558,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3553,11 +3580,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3575,11 +3602,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3597,11 +3624,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3619,11 +3646,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3641,11 +3668,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3663,11 +3690,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3685,11 +3712,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3707,11 +3734,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3729,11 +3756,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3751,11 +3778,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3773,11 +3800,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3795,11 +3822,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3817,11 +3844,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3839,11 +3866,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3861,11 +3888,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3883,11 +3910,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3905,11 +3932,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3927,11 +3954,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3949,11 +3976,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3971,11 +3998,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3993,11 +4020,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -4015,11 +4042,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -4037,11 +4064,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -4059,11 +4086,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -4081,11 +4108,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -4103,11 +4130,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -4125,11 +4152,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -4147,11 +4174,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -4169,11 +4196,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -4191,11 +4218,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -4213,11 +4240,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4235,11 +4262,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4257,11 +4284,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4279,11 +4306,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4301,11 +4328,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4323,11 +4350,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4345,11 +4372,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4367,11 +4394,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4389,11 +4416,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4411,11 +4438,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4433,11 +4460,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4455,11 +4482,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4477,11 +4504,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4499,11 +4526,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4521,11 +4548,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4543,11 +4570,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4565,11 +4592,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="48">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="50">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="49">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="51">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4587,11 +4614,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4609,11 +4636,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4631,11 +4658,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4653,11 +4680,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4675,11 +4702,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4697,11 +4724,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4719,11 +4746,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4741,11 +4768,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4763,11 +4790,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4785,11 +4812,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4807,11 +4834,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4829,11 +4856,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4851,11 +4878,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4873,11 +4900,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4895,11 +4922,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4917,11 +4944,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4939,11 +4966,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4961,11 +4988,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -4983,11 +5010,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -5005,11 +5032,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -5027,11 +5054,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -5049,11 +5076,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -5071,11 +5098,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -5093,11 +5120,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -5115,11 +5142,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -5137,11 +5164,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -5159,11 +5186,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5181,11 +5208,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5203,11 +5230,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5225,11 +5252,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5247,11 +5274,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5269,11 +5296,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5291,11 +5318,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5313,11 +5340,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5335,11 +5362,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5357,11 +5384,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5379,11 +5406,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5401,11 +5428,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5423,11 +5450,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5445,11 +5472,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5467,11 +5494,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5489,11 +5516,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5511,11 +5538,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5533,11 +5560,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5555,11 +5582,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5577,11 +5604,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5599,11 +5626,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5621,11 +5648,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5643,11 +5670,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5665,11 +5692,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5687,11 +5714,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5709,11 +5736,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5731,11 +5758,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5753,11 +5780,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5775,11 +5802,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5797,11 +5824,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5819,11 +5846,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5841,11 +5868,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5863,11 +5890,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5885,11 +5912,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5907,11 +5934,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5929,11 +5956,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5951,11 +5978,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -5973,11 +6000,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="50">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="52">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="51">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="53">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -5995,11 +6022,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -6017,11 +6044,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -6039,11 +6066,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -6061,11 +6088,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -6083,11 +6110,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -6105,11 +6132,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -6127,11 +6154,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -6149,11 +6176,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -6171,11 +6198,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6193,11 +6220,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6215,11 +6242,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6237,11 +6264,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6259,11 +6286,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6281,11 +6308,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6303,11 +6330,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6325,11 +6352,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6347,11 +6374,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6369,11 +6396,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6391,11 +6418,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6413,11 +6440,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6435,11 +6462,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6457,11 +6484,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6479,11 +6506,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6501,11 +6528,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6523,11 +6550,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6545,11 +6572,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6567,11 +6594,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6589,11 +6616,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6611,11 +6638,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6633,11 +6660,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6655,11 +6682,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6677,11 +6704,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6699,11 +6726,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6721,11 +6748,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6743,11 +6770,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6765,11 +6792,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6787,11 +6814,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6809,11 +6836,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6831,11 +6858,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6853,11 +6880,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6875,11 +6902,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6897,11 +6924,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6919,11 +6946,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6941,11 +6968,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6963,11 +6990,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -6985,11 +7012,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -7007,11 +7034,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -7029,11 +7056,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -7051,11 +7078,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -7073,11 +7100,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -7095,11 +7122,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -7117,11 +7144,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -7139,11 +7166,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -7161,11 +7188,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7183,11 +7210,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7205,11 +7232,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7227,11 +7254,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7249,11 +7276,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7271,11 +7298,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7293,11 +7320,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7315,11 +7342,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7337,11 +7364,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7359,11 +7386,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7381,11 +7408,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="52">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="54">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="53">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="55">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7403,11 +7430,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7425,11 +7452,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7447,11 +7474,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7469,11 +7496,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7491,11 +7518,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7513,11 +7540,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7535,11 +7562,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7557,11 +7584,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7579,11 +7606,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7601,11 +7628,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7623,11 +7650,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7645,11 +7672,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7667,11 +7694,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7689,11 +7716,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7711,11 +7738,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7733,11 +7760,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7755,11 +7782,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7777,11 +7804,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7799,11 +7826,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7821,11 +7848,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7843,11 +7870,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7865,11 +7892,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7887,11 +7914,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7909,11 +7936,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7931,11 +7958,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7953,11 +7980,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -7975,11 +8002,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -7997,11 +8024,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -8019,11 +8046,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -8041,11 +8068,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -8063,11 +8090,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -8085,11 +8112,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -8107,11 +8134,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -8129,11 +8156,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -8151,11 +8178,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -8173,11 +8200,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8195,11 +8222,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8217,11 +8244,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8239,11 +8266,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8261,11 +8288,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8283,11 +8310,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8305,11 +8332,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8327,11 +8354,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8349,11 +8376,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8371,11 +8398,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8393,11 +8420,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8415,11 +8442,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8437,11 +8464,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8459,11 +8486,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8481,11 +8508,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8503,11 +8530,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8525,11 +8552,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8547,11 +8574,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8569,11 +8596,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8591,11 +8618,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8613,11 +8640,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8635,11 +8662,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8657,11 +8684,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8679,11 +8706,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8701,11 +8728,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8723,11 +8750,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8745,11 +8772,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8767,11 +8794,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8789,11 +8816,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="54">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="56">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="55">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="57">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8811,11 +8838,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8833,11 +8860,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8855,11 +8882,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8877,11 +8904,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8899,11 +8926,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8921,11 +8948,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8943,11 +8970,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8965,11 +8992,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -8987,11 +9014,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -9009,11 +9036,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -9031,11 +9058,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -9053,11 +9080,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -9075,11 +9102,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -9097,11 +9124,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -9119,11 +9146,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -9141,11 +9168,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -9163,11 +9190,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9185,11 +9212,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9207,11 +9234,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9229,11 +9256,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9251,11 +9278,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9273,11 +9300,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9295,11 +9322,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9317,11 +9344,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9339,11 +9366,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9361,11 +9388,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9383,11 +9410,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9405,11 +9432,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9427,11 +9454,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9449,11 +9476,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9471,11 +9498,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9493,11 +9520,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9515,11 +9542,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9537,11 +9564,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9559,11 +9586,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9581,11 +9608,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9603,11 +9630,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9625,11 +9652,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9647,11 +9674,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9669,11 +9696,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9691,11 +9718,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9713,11 +9740,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9735,11 +9762,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9757,11 +9784,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9779,11 +9806,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9801,11 +9828,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9823,11 +9850,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9845,11 +9872,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9867,11 +9894,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9889,11 +9916,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9911,11 +9938,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9933,11 +9960,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9955,11 +9982,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -9977,11 +10004,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -9999,11 +10026,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -10021,11 +10048,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -10043,11 +10070,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -10065,11 +10092,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -10087,11 +10114,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -10109,11 +10136,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10131,11 +10158,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10153,11 +10180,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10175,11 +10202,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10197,11 +10224,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="56">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="58">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="57">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="59">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10219,11 +10246,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10241,11 +10268,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10263,11 +10290,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10285,11 +10312,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10307,11 +10334,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10329,11 +10356,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10351,11 +10378,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10373,11 +10400,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10395,11 +10422,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10417,11 +10444,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10439,11 +10466,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/12626731.xlsx
+++ b/12626731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHIVEN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122F94BD-4816-43E6-A12D-003D29EF598B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4F2BF3-A7D0-426D-96E6-8C6E6598A8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>Today, I worked on Coding.</t>
   </si>
 </sst>
 </file>
@@ -2426,27 +2429,51 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="8"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="12"/>
+    <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B36" s="14">
+        <v>450</v>
+      </c>
+      <c r="C36" s="14">
+        <v>20</v>
+      </c>
+      <c r="D36" s="14">
+        <v>0</v>
+      </c>
+      <c r="E36" s="14">
+        <v>90</v>
+      </c>
+      <c r="F36" s="14">
+        <v>200</v>
+      </c>
+      <c r="G36" s="14">
+        <v>4</v>
+      </c>
+      <c r="H36" s="14">
+        <v>270</v>
+      </c>
+      <c r="I36" s="15">
+        <f t="shared" ref="I36" si="48">IF(SUM(B36:F36,H36)=0,"",SUM(B36:F36,H36))</f>
+        <v>1030</v>
+      </c>
+      <c r="J36" s="15">
+        <f t="shared" ref="J36" si="49">IF(I36="","",1440-I36)</f>
+        <v>410</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>
@@ -3184,11 +3211,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="48">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="50">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="49">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="51">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3206,11 +3233,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3228,11 +3255,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3250,11 +3277,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3272,11 +3299,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3294,11 +3321,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3316,11 +3343,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3338,11 +3365,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3360,11 +3387,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3382,11 +3409,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3404,11 +3431,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3426,11 +3453,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3448,11 +3475,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3470,11 +3497,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3492,11 +3519,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3514,11 +3541,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3536,11 +3563,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3558,11 +3585,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3580,11 +3607,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3602,11 +3629,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3624,11 +3651,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3646,11 +3673,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3668,11 +3695,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3690,11 +3717,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3712,11 +3739,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3734,11 +3761,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3756,11 +3783,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3778,11 +3805,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3800,11 +3827,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3822,11 +3849,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3844,11 +3871,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3866,11 +3893,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3888,11 +3915,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3910,11 +3937,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3932,11 +3959,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3954,11 +3981,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3976,11 +4003,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3998,11 +4025,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -4020,11 +4047,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -4042,11 +4069,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -4064,11 +4091,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -4086,11 +4113,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -4108,11 +4135,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -4130,11 +4157,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -4152,11 +4179,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -4174,11 +4201,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -4196,11 +4223,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -4218,11 +4245,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -4240,11 +4267,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -4262,11 +4289,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4284,11 +4311,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4306,11 +4333,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
@@ -4328,11 +4355,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4350,11 +4377,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4372,11 +4399,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4394,11 +4421,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4416,11 +4443,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4438,11 +4465,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4460,11 +4487,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4482,11 +4509,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4504,11 +4531,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4526,11 +4553,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4548,11 +4575,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4570,11 +4597,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4592,11 +4619,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="50">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="52">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="51">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="53">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4614,11 +4641,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4636,11 +4663,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4658,11 +4685,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4680,11 +4707,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4702,11 +4729,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4724,11 +4751,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4746,11 +4773,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4768,11 +4795,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4790,11 +4817,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4812,11 +4839,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4834,11 +4861,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4856,11 +4883,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4878,11 +4905,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -4900,11 +4927,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -4922,11 +4949,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -4944,11 +4971,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -4966,11 +4993,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -4988,11 +5015,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -5010,11 +5037,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -5032,11 +5059,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -5054,11 +5081,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -5076,11 +5103,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -5098,11 +5125,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -5120,11 +5147,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -5142,11 +5169,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -5164,11 +5191,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -5186,11 +5213,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5208,11 +5235,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5230,11 +5257,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5252,11 +5279,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5274,11 +5301,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5296,11 +5323,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5318,11 +5345,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5340,11 +5367,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5362,11 +5389,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5384,11 +5411,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5406,11 +5433,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5428,11 +5455,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5450,11 +5477,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5472,11 +5499,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5494,11 +5521,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5516,11 +5543,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5538,11 +5565,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5560,11 +5587,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5582,11 +5609,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5604,11 +5631,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5626,11 +5653,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5648,11 +5675,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5670,11 +5697,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5692,11 +5719,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5714,11 +5741,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5736,11 +5763,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5758,11 +5785,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5780,11 +5807,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5802,11 +5829,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5824,11 +5851,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5846,11 +5873,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5868,11 +5895,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -5890,11 +5917,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -5912,11 +5939,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -5934,11 +5961,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -5956,11 +5983,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -5978,11 +6005,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -6000,11 +6027,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="52">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="54">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="53">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="55">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -6022,11 +6049,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -6044,11 +6071,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -6066,11 +6093,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -6088,11 +6115,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -6110,11 +6137,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -6132,11 +6159,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -6154,11 +6181,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -6176,11 +6203,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -6198,11 +6225,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6220,11 +6247,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6242,11 +6269,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6264,11 +6291,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6286,11 +6313,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6308,11 +6335,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6330,11 +6357,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6352,11 +6379,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6374,11 +6401,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6396,11 +6423,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6418,11 +6445,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6440,11 +6467,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6462,11 +6489,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6484,11 +6511,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6506,11 +6533,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6528,11 +6555,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6550,11 +6577,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6572,11 +6599,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6594,11 +6621,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6616,11 +6643,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6638,11 +6665,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6660,11 +6687,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6682,11 +6709,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6704,11 +6731,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6726,11 +6753,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6748,11 +6775,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6770,11 +6797,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6792,11 +6819,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6814,11 +6841,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6836,11 +6863,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6858,11 +6885,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6880,11 +6907,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -6902,11 +6929,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -6924,11 +6951,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -6946,11 +6973,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -6968,11 +6995,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -6990,11 +7017,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -7012,11 +7039,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -7034,11 +7061,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -7056,11 +7083,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -7078,11 +7105,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -7100,11 +7127,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -7122,11 +7149,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -7144,11 +7171,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -7166,11 +7193,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -7188,11 +7215,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7210,11 +7237,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7232,11 +7259,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7254,11 +7281,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7276,11 +7303,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7298,11 +7325,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7320,11 +7347,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7342,11 +7369,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7364,11 +7391,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7386,11 +7413,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7408,11 +7435,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="54">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="56">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="55">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="57">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7430,11 +7457,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7452,11 +7479,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7474,11 +7501,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7496,11 +7523,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7518,11 +7545,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7540,11 +7567,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7562,11 +7589,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7584,11 +7611,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7606,11 +7633,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7628,11 +7655,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7650,11 +7677,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7672,11 +7699,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7694,11 +7721,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7716,11 +7743,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7738,11 +7765,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7760,11 +7787,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7782,11 +7809,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7804,11 +7831,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7826,11 +7853,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7848,11 +7875,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7870,11 +7897,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -7892,11 +7919,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -7914,11 +7941,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -7936,11 +7963,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -7958,11 +7985,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -7980,11 +8007,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -8002,11 +8029,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -8024,11 +8051,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -8046,11 +8073,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -8068,11 +8095,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -8090,11 +8117,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -8112,11 +8139,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -8134,11 +8161,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -8156,11 +8183,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -8178,11 +8205,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -8200,11 +8227,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8222,11 +8249,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8244,11 +8271,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8266,11 +8293,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8288,11 +8315,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8310,11 +8337,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8332,11 +8359,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8354,11 +8381,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8376,11 +8403,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8398,11 +8425,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8420,11 +8447,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8442,11 +8469,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8464,11 +8491,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8486,11 +8513,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8508,11 +8535,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8530,11 +8557,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8552,11 +8579,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8574,11 +8601,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8596,11 +8623,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8618,11 +8645,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8640,11 +8667,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8662,11 +8689,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8684,11 +8711,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8706,11 +8733,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8728,11 +8755,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8750,11 +8777,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8772,11 +8799,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8794,11 +8821,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8816,11 +8843,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="56">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="58">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="57">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="59">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8838,11 +8865,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8860,11 +8887,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8882,11 +8909,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -8904,11 +8931,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -8926,11 +8953,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -8948,11 +8975,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -8970,11 +8997,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -8992,11 +9019,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -9014,11 +9041,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -9036,11 +9063,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -9058,11 +9085,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -9080,11 +9107,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -9102,11 +9129,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -9124,11 +9151,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -9146,11 +9173,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -9168,11 +9195,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -9190,11 +9217,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9212,11 +9239,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9234,11 +9261,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9256,11 +9283,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9278,11 +9305,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9300,11 +9327,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9322,11 +9349,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9344,11 +9371,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9366,11 +9393,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9388,11 +9415,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9410,11 +9437,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9432,11 +9459,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9454,11 +9481,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9476,11 +9503,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9498,11 +9525,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9520,11 +9547,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9542,11 +9569,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9564,11 +9591,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9586,11 +9613,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9608,11 +9635,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9630,11 +9657,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9652,11 +9679,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9674,11 +9701,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9696,11 +9723,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9718,11 +9745,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9740,11 +9767,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9762,11 +9789,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9784,11 +9811,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9806,11 +9833,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9828,11 +9855,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9850,11 +9877,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9872,11 +9899,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -9894,11 +9921,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -9916,11 +9943,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -9938,11 +9965,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -9960,11 +9987,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -9982,11 +10009,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -10004,11 +10031,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -10026,11 +10053,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -10048,11 +10075,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -10070,11 +10097,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -10092,11 +10119,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -10114,11 +10141,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -10136,11 +10163,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10158,11 +10185,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10180,11 +10207,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10202,11 +10229,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10224,11 +10251,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="58">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="60">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="59">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="61">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10246,11 +10273,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10268,11 +10295,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10290,11 +10317,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10312,11 +10339,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10334,11 +10361,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10356,11 +10383,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10378,11 +10405,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10400,11 +10427,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10422,11 +10449,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10444,11 +10471,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10466,11 +10493,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="K401" s="11"/>
